--- a/attached_assets/flowforge-seed-import.xlsx
+++ b/attached_assets/flowforge-seed-import.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="194">
   <si>
     <t>name</t>
   </si>
@@ -33,6 +33,57 @@
     <t>paymentTerms</t>
   </si>
   <si>
+    <t>Required. Company name</t>
+  </si>
+  <si>
+    <t>2-letter code (CN, VN…)</t>
+  </si>
+  <si>
+    <t>Contact person</t>
+  </si>
+  <si>
+    <t>Contact email</t>
+  </si>
+  <si>
+    <t>WhatsApp number</t>
+  </si>
+  <si>
+    <t>Payment terms</t>
+  </si>
+  <si>
+    <t>Tianjin Wire Works</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Guangzhou Metalworks</t>
+  </si>
+  <si>
+    <t>Foshan Precision Parts</t>
+  </si>
+  <si>
+    <t>Foshan LightMaster</t>
+  </si>
+  <si>
+    <t>Shenzhen LEDPro</t>
+  </si>
+  <si>
+    <t>Dongguan BrightTech</t>
+  </si>
+  <si>
+    <t>Hangzhou Timber Co.</t>
+  </si>
+  <si>
+    <t>Ningbo Hardwood Mill</t>
+  </si>
+  <si>
+    <t>Qingdao Packaging Group</t>
+  </si>
+  <si>
     <t>poNumber</t>
   </si>
   <si>
@@ -78,6 +129,372 @@
     <t>targetSpreadPct</t>
   </si>
   <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Buyer PO / deal ref</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Required — must match Suppliers tab</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>OCEAN|AIR|LCL|COURIER</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>spec|quotes|sample_ord|…|delivered</t>
+  </si>
+  <si>
+    <t>Buyer total $</t>
+  </si>
+  <si>
+    <t>Unit price $</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Target spread %</t>
+  </si>
+  <si>
+    <t>PO-1001-778143</t>
+  </si>
+  <si>
+    <t>BMAS-2026-001</t>
+  </si>
+  <si>
+    <t>Chrome Retail Hanger — Heavy Duty Top</t>
+  </si>
+  <si>
+    <t>Chrome Retail Hanger</t>
+  </si>
+  <si>
+    <t>Marlowe &amp; Sons</t>
+  </si>
+  <si>
+    <t>OCEAN</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>spec</t>
+  </si>
+  <si>
+    <t>PO-1002-783656</t>
+  </si>
+  <si>
+    <t>BVS-2026-001</t>
+  </si>
+  <si>
+    <t>Chrome Retail Hanger — Slim Profile Bottom</t>
+  </si>
+  <si>
+    <t>Vellum Studio</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>quotes</t>
+  </si>
+  <si>
+    <t>PO-1003-F18SAF0259</t>
+  </si>
+  <si>
+    <t>Chrome Retail Hanger — Velvet Grip</t>
+  </si>
+  <si>
+    <t>Greece</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>sample_ord</t>
+  </si>
+  <si>
+    <t>PO-1004-792884</t>
+  </si>
+  <si>
+    <t>Chrome Retail Hanger — Notched Shoulder</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>sample_apr</t>
+  </si>
+  <si>
+    <t>PO-1005-797758-001</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>po_issued</t>
+  </si>
+  <si>
+    <t>PO-1006-P201466120</t>
+  </si>
+  <si>
+    <t>BNBO-2026-001</t>
+  </si>
+  <si>
+    <t>Powder-Coat Hanger — Charcoal Bottom</t>
+  </si>
+  <si>
+    <t>Powder-Coat Hanger</t>
+  </si>
+  <si>
+    <t>Northbound Outfitters</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>PO-1007-P201472890</t>
+  </si>
+  <si>
+    <t>BMAS-2026-002</t>
+  </si>
+  <si>
+    <t>Powder-Coat Hanger — Bronze Petite</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>qc</t>
+  </si>
+  <si>
+    <t>PO-1008-P201475383</t>
+  </si>
+  <si>
+    <t>Powder-Coat Hanger — Ivory Wishbone</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>ex_factory</t>
+  </si>
+  <si>
+    <t>PO-1009-711872</t>
+  </si>
+  <si>
+    <t>Powder-Coat Hanger — Matte Black Top</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>in_transit</t>
+  </si>
+  <si>
+    <t>PO-1010-4500096501</t>
+  </si>
+  <si>
+    <t>BAN-2026-001</t>
+  </si>
+  <si>
+    <t>LED Track Light — 3000K Spot — 12W</t>
+  </si>
+  <si>
+    <t>LED Track Light</t>
+  </si>
+  <si>
+    <t>Atelier Nord</t>
+  </si>
+  <si>
+    <t>AIR</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>payment</t>
+  </si>
+  <si>
+    <t>PO-1011-4500110188</t>
+  </si>
+  <si>
+    <t>BPGC-2026-001</t>
+  </si>
+  <si>
+    <t>LED Track Light — 4000K Wash — 18W</t>
+  </si>
+  <si>
+    <t>Pioneer Goods Co.</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>delivered</t>
+  </si>
+  <si>
+    <t>PO-1012-4500110188</t>
+  </si>
+  <si>
+    <t>LED Track Light — Tunable White — 24W</t>
+  </si>
+  <si>
+    <t>PO-1013-4500010009 R</t>
+  </si>
+  <si>
+    <t>BNBO-2026-002</t>
+  </si>
+  <si>
+    <t>LED Display Cabinet — Warm White Strip — 1.2m</t>
+  </si>
+  <si>
+    <t>LED Display Cabinet</t>
+  </si>
+  <si>
+    <t>Shanghai</t>
+  </si>
+  <si>
+    <t>PO-1014-4500010022</t>
+  </si>
+  <si>
+    <t>BVS-2026-002</t>
+  </si>
+  <si>
+    <t>LED Display Cabinet — Cool White Bar — 900mm</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>PO-1015-4500032038</t>
+  </si>
+  <si>
+    <t>LED Display Cabinet — RGB Edge — 1.8m</t>
+  </si>
+  <si>
+    <t>PO-1016-4500030233</t>
+  </si>
+  <si>
+    <t>LED Display Cabinet — Tunable Halo — 600mm</t>
+  </si>
+  <si>
+    <t>PO-1017-F21-MB-002-1</t>
+  </si>
+  <si>
+    <t>Thailand</t>
+  </si>
+  <si>
+    <t>PO-1018-4500087059</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>PO-1019-P200920425</t>
+  </si>
+  <si>
+    <t>BPGC-2026-002</t>
+  </si>
+  <si>
+    <t>Engineered Oak Flooring — Chevron — Whitewash</t>
+  </si>
+  <si>
+    <t>Engineered Oak Flooring</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>PO-1020-P201353881</t>
+  </si>
+  <si>
+    <t>BCHH-2026-001</t>
+  </si>
+  <si>
+    <t>Engineered Oak Flooring — Plank — Coffee</t>
+  </si>
+  <si>
+    <t>Cedar Hollow Homes</t>
+  </si>
+  <si>
+    <t>PO-1021-P201356135</t>
+  </si>
+  <si>
+    <t>Engineered Oak Flooring — Herringbone — Natural</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>PO-1022-P201357730</t>
+  </si>
+  <si>
+    <t>Engineered Oak Flooring — Plank — Smoked</t>
+  </si>
+  <si>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>PO-1023-P201466769</t>
+  </si>
+  <si>
+    <t>BVS-2026-003</t>
+  </si>
+  <si>
+    <t>Cardboard Mailer — Recycled Kraft 9x12</t>
+  </si>
+  <si>
+    <t>Cardboard Mailer</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>PO-1024-4500011121</t>
+  </si>
+  <si>
+    <t>BCHH-2026-002</t>
+  </si>
+  <si>
+    <t>Cardboard Mailer — Tear-Strip 12x15</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
     <t>label</t>
   </si>
   <si>
@@ -91,13 +508,100 @@
   </si>
   <si>
     <t>sortOrder</t>
+  </si>
+  <si>
+    <t>Must match a Shipments poNumber</t>
+  </si>
+  <si>
+    <t>Payment milestone label</t>
+  </si>
+  <si>
+    <t>Amount USD</t>
+  </si>
+  <si>
+    <t>% of total (0-100)</t>
+  </si>
+  <si>
+    <t>TRUE or FALSE</t>
+  </si>
+  <si>
+    <t>0, 1, 2…</t>
+  </si>
+  <si>
+    <t>Deposit (30%)</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>Balance (70%)</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -107,6 +611,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF94A3B8"/>
     </font>
   </fonts>
   <fills count="3">
@@ -134,9 +642,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -486,7 +995,7 @@
     <col min="5" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,6 +1013,206 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -514,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -532,51 +1241,1226 @@
     <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3">
+        <v>46234</v>
+      </c>
+      <c r="M3">
+        <v>5.2</v>
+      </c>
+      <c r="N3">
+        <v>9500</v>
+      </c>
+      <c r="O3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4">
+        <v>35048</v>
+      </c>
+      <c r="M4">
+        <v>2.85</v>
+      </c>
+      <c r="N4">
+        <v>12000</v>
+      </c>
+      <c r="O4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5">
+        <v>46234</v>
+      </c>
+      <c r="M5">
+        <v>5.2</v>
+      </c>
+      <c r="N5">
+        <v>9500</v>
+      </c>
+      <c r="O5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6">
+        <v>35048</v>
+      </c>
+      <c r="M6">
+        <v>2.85</v>
+      </c>
+      <c r="N6">
+        <v>12000</v>
+      </c>
+      <c r="O6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7">
+        <v>46234</v>
+      </c>
+      <c r="M7">
+        <v>5.2</v>
+      </c>
+      <c r="N7">
+        <v>9500</v>
+      </c>
+      <c r="O7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8">
+        <v>27477</v>
+      </c>
+      <c r="M8">
+        <v>4.6</v>
+      </c>
+      <c r="N8">
+        <v>6000</v>
+      </c>
+      <c r="O8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" t="s">
+        <v>92</v>
+      </c>
+      <c r="K9" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9">
+        <v>30492</v>
+      </c>
+      <c r="M9">
+        <v>6.2</v>
+      </c>
+      <c r="N9">
+        <v>5000</v>
+      </c>
+      <c r="O9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L10">
+        <v>27477</v>
+      </c>
+      <c r="M10">
+        <v>4.6</v>
+      </c>
+      <c r="N10">
+        <v>6000</v>
+      </c>
+      <c r="O10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" t="s">
+        <v>102</v>
+      </c>
+      <c r="L11">
+        <v>30492</v>
+      </c>
+      <c r="M11">
+        <v>6.2</v>
+      </c>
+      <c r="N11">
+        <v>5000</v>
+      </c>
+      <c r="O11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12">
+        <v>24978</v>
+      </c>
+      <c r="M12">
+        <v>24.5</v>
+      </c>
+      <c r="N12">
+        <v>900</v>
+      </c>
+      <c r="O12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" t="s">
+        <v>115</v>
+      </c>
+      <c r="J13" t="s">
+        <v>115</v>
+      </c>
+      <c r="K13" t="s">
+        <v>116</v>
+      </c>
+      <c r="L13">
+        <v>11567</v>
+      </c>
+      <c r="M13">
+        <v>13.2</v>
+      </c>
+      <c r="N13">
+        <v>880</v>
+      </c>
+      <c r="O13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14">
+        <v>24978</v>
+      </c>
+      <c r="M14">
+        <v>24.5</v>
+      </c>
+      <c r="N14">
+        <v>900</v>
+      </c>
+      <c r="O14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15">
+        <v>25702</v>
+      </c>
+      <c r="M15">
+        <v>14.8</v>
+      </c>
+      <c r="N15">
+        <v>1800</v>
+      </c>
+      <c r="O15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="F16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" t="s">
+        <v>127</v>
+      </c>
+      <c r="I16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L16">
+        <v>33699</v>
+      </c>
+      <c r="M16">
+        <v>18.5</v>
+      </c>
+      <c r="N16">
+        <v>1800</v>
+      </c>
+      <c r="O16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="F17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" t="s">
+        <v>127</v>
+      </c>
+      <c r="I17" t="s">
+        <v>75</v>
+      </c>
+      <c r="J17" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17" t="s">
+        <v>76</v>
+      </c>
+      <c r="L17">
+        <v>25702</v>
+      </c>
+      <c r="M17">
+        <v>14.8</v>
+      </c>
+      <c r="N17">
+        <v>1800</v>
+      </c>
+      <c r="O17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" t="s">
+        <v>127</v>
+      </c>
+      <c r="I18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J18" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" t="s">
+        <v>79</v>
+      </c>
+      <c r="L18">
+        <v>33699</v>
+      </c>
+      <c r="M18">
+        <v>18.5</v>
+      </c>
+      <c r="N18">
+        <v>1800</v>
+      </c>
+      <c r="O18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" t="s">
+        <v>86</v>
+      </c>
+      <c r="K19" t="s">
+        <v>87</v>
+      </c>
+      <c r="L19">
+        <v>25702</v>
+      </c>
+      <c r="M19">
+        <v>14.8</v>
+      </c>
+      <c r="N19">
+        <v>1800</v>
+      </c>
+      <c r="O19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" t="s">
+        <v>135</v>
+      </c>
+      <c r="I20" t="s">
+        <v>92</v>
+      </c>
+      <c r="J20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K20" t="s">
+        <v>93</v>
+      </c>
+      <c r="L20">
+        <v>33699</v>
+      </c>
+      <c r="M20">
+        <v>18.5</v>
+      </c>
+      <c r="N20">
+        <v>1800</v>
+      </c>
+      <c r="O20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" t="s">
         <v>20</v>
+      </c>
+      <c r="F21" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J21" t="s">
+        <v>97</v>
+      </c>
+      <c r="K21" t="s">
+        <v>98</v>
+      </c>
+      <c r="L21">
+        <v>112840</v>
+      </c>
+      <c r="M21">
+        <v>4.8</v>
+      </c>
+      <c r="N21">
+        <v>22250</v>
+      </c>
+      <c r="O21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>144</v>
+      </c>
+      <c r="G22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" t="s">
+        <v>101</v>
+      </c>
+      <c r="J22" t="s">
+        <v>101</v>
+      </c>
+      <c r="K22" t="s">
+        <v>102</v>
+      </c>
+      <c r="L22">
+        <v>146688</v>
+      </c>
+      <c r="M22">
+        <v>6.2</v>
+      </c>
+      <c r="N22">
+        <v>23000</v>
+      </c>
+      <c r="O22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" t="s">
+        <v>147</v>
+      </c>
+      <c r="I23" t="s">
+        <v>109</v>
+      </c>
+      <c r="J23" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23">
+        <v>112840</v>
+      </c>
+      <c r="M23">
+        <v>4.8</v>
+      </c>
+      <c r="N23">
+        <v>22250</v>
+      </c>
+      <c r="O23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24" t="s">
+        <v>115</v>
+      </c>
+      <c r="J24" t="s">
+        <v>115</v>
+      </c>
+      <c r="K24" t="s">
+        <v>116</v>
+      </c>
+      <c r="L24">
+        <v>146688</v>
+      </c>
+      <c r="M24">
+        <v>6.2</v>
+      </c>
+      <c r="N24">
+        <v>23000</v>
+      </c>
+      <c r="O24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" t="s">
+        <v>155</v>
+      </c>
+      <c r="I25" t="s">
+        <v>58</v>
+      </c>
+      <c r="J25" t="s">
+        <v>58</v>
+      </c>
+      <c r="K25" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25">
+        <v>19500</v>
+      </c>
+      <c r="M25">
+        <v>4.1</v>
+      </c>
+      <c r="N25">
+        <v>4800</v>
+      </c>
+      <c r="O25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" t="s">
+        <v>154</v>
+      </c>
+      <c r="E26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" t="s">
+        <v>65</v>
+      </c>
+      <c r="J26" t="s">
+        <v>65</v>
+      </c>
+      <c r="K26" t="s">
+        <v>66</v>
+      </c>
+      <c r="L26">
+        <v>24938</v>
+      </c>
+      <c r="M26">
+        <v>3.2</v>
+      </c>
+      <c r="N26">
+        <v>7800</v>
+      </c>
+      <c r="O26" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -587,7 +2471,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -599,27 +2483,1154 @@
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3">
+        <v>2280</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4">
+        <v>5320</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5">
+        <v>3090</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6">
+        <v>7210</v>
+      </c>
+      <c r="D6">
+        <v>70</v>
+      </c>
+      <c r="E6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7">
+        <v>3996</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8">
+        <v>9324</v>
+      </c>
+      <c r="D8">
+        <v>70</v>
+      </c>
+      <c r="E8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9">
+        <v>4998</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10">
+        <v>11662</v>
+      </c>
+      <c r="D10">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11">
+        <v>4560</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12">
+        <v>10640</v>
+      </c>
+      <c r="D12">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>172</v>
+      </c>
+      <c r="F12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13">
+        <v>2340</v>
+      </c>
+      <c r="D13">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" t="s">
+        <v>183</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14">
+        <v>5460</v>
+      </c>
+      <c r="D14">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F14" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15">
+        <v>3150</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>180</v>
+      </c>
+      <c r="F15" t="s">
+        <v>185</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16">
+        <v>7350</v>
+      </c>
+      <c r="D16">
+        <v>70</v>
+      </c>
+      <c r="E16" t="s">
+        <v>172</v>
+      </c>
+      <c r="F16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17">
+        <v>4050</v>
+      </c>
+      <c r="D17">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F17" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18">
+        <v>9450</v>
+      </c>
+      <c r="D18">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F18" t="s">
+        <v>188</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19">
+        <v>3780</v>
+      </c>
+      <c r="D19">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>180</v>
+      </c>
+      <c r="F19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20">
+        <v>8820</v>
+      </c>
+      <c r="D20">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21">
+        <v>2085</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>180</v>
+      </c>
+      <c r="F21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22">
+        <v>4865</v>
+      </c>
+      <c r="D22">
+        <v>70</v>
+      </c>
+      <c r="E22" t="s">
+        <v>180</v>
+      </c>
+      <c r="F22" t="s">
+        <v>191</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23">
+        <v>2754</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>180</v>
+      </c>
+      <c r="F23" t="s">
+        <v>192</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24">
+        <v>6426</v>
+      </c>
+      <c r="D24">
+        <v>70</v>
+      </c>
+      <c r="E24" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24" t="s">
+        <v>193</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25">
+        <v>3507</v>
+      </c>
+      <c r="D25">
+        <v>30</v>
+      </c>
+      <c r="E25" t="s">
+        <v>172</v>
+      </c>
+      <c r="F25" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26">
+        <v>8183</v>
+      </c>
+      <c r="D26">
+        <v>70</v>
+      </c>
+      <c r="E26" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27">
+        <v>1512</v>
+      </c>
+      <c r="D27">
+        <v>30</v>
+      </c>
+      <c r="E27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F27" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28">
+        <v>3528</v>
+      </c>
+      <c r="D28">
+        <v>70</v>
+      </c>
+      <c r="E28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F28" t="s">
+        <v>176</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29">
+        <v>2138</v>
+      </c>
+      <c r="D29">
+        <v>30</v>
+      </c>
+      <c r="E29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" t="s">
+        <v>177</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30">
+        <v>4987</v>
+      </c>
+      <c r="D30">
+        <v>70</v>
+      </c>
+      <c r="E30" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31">
+        <v>2862</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32">
+        <v>6678</v>
+      </c>
+      <c r="D32">
+        <v>70</v>
+      </c>
+      <c r="E32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" t="s">
+        <v>179</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33">
+        <v>3686</v>
+      </c>
+      <c r="D33">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" t="s">
+        <v>181</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34">
+        <v>8599</v>
+      </c>
+      <c r="D34">
+        <v>70</v>
+      </c>
+      <c r="E34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35">
+        <v>1512</v>
+      </c>
+      <c r="D35">
+        <v>30</v>
+      </c>
+      <c r="E35" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" t="s">
+        <v>174</v>
+      </c>
+      <c r="C36">
+        <v>3528</v>
+      </c>
+      <c r="D36">
+        <v>70</v>
+      </c>
+      <c r="E36" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" t="s">
+        <v>184</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37">
+        <v>2138</v>
+      </c>
+      <c r="D37">
+        <v>30</v>
+      </c>
+      <c r="E37" t="s">
+        <v>180</v>
+      </c>
+      <c r="F37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" t="s">
+        <v>174</v>
+      </c>
+      <c r="C38">
+        <v>4987</v>
+      </c>
+      <c r="D38">
+        <v>70</v>
+      </c>
+      <c r="E38" t="s">
+        <v>172</v>
+      </c>
+      <c r="F38" t="s">
+        <v>186</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39">
+        <v>16920</v>
+      </c>
+      <c r="D39">
+        <v>30</v>
+      </c>
+      <c r="E39" t="s">
+        <v>180</v>
+      </c>
+      <c r="F39" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40">
+        <v>39480</v>
+      </c>
+      <c r="D40">
+        <v>70</v>
+      </c>
+      <c r="E40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" t="s">
+        <v>188</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41">
+        <v>21630</v>
+      </c>
+      <c r="D41">
+        <v>30</v>
+      </c>
+      <c r="E41" t="s">
+        <v>180</v>
+      </c>
+      <c r="F41" t="s">
+        <v>189</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>141</v>
+      </c>
+      <c r="B42" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42">
+        <v>50470</v>
+      </c>
+      <c r="D42">
+        <v>70</v>
+      </c>
+      <c r="E42" t="s">
+        <v>180</v>
+      </c>
+      <c r="F42" t="s">
+        <v>109</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43">
+        <v>9120</v>
+      </c>
+      <c r="D43">
+        <v>30</v>
+      </c>
+      <c r="E43" t="s">
+        <v>180</v>
+      </c>
+      <c r="F43" t="s">
+        <v>190</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>145</v>
+      </c>
+      <c r="B44" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44">
+        <v>21280</v>
+      </c>
+      <c r="D44">
+        <v>70</v>
+      </c>
+      <c r="E44" t="s">
+        <v>172</v>
+      </c>
+      <c r="F44" t="s">
+        <v>191</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>148</v>
+      </c>
+      <c r="B45" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45">
+        <v>12750</v>
+      </c>
+      <c r="D45">
+        <v>30</v>
+      </c>
+      <c r="E45" t="s">
+        <v>180</v>
+      </c>
+      <c r="F45" t="s">
+        <v>192</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46">
+        <v>29750</v>
+      </c>
+      <c r="D46">
+        <v>70</v>
+      </c>
+      <c r="E46" t="s">
+        <v>180</v>
+      </c>
+      <c r="F46" t="s">
+        <v>193</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47">
+        <v>4680</v>
+      </c>
+      <c r="D47">
+        <v>30</v>
+      </c>
+      <c r="E47" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" t="s">
+        <v>173</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" t="s">
+        <v>174</v>
+      </c>
+      <c r="C48">
+        <v>10920</v>
+      </c>
+      <c r="D48">
+        <v>70</v>
+      </c>
+      <c r="E48" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" t="s">
+        <v>65</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49">
+        <v>5985</v>
+      </c>
+      <c r="D49">
+        <v>30</v>
+      </c>
+      <c r="E49" t="s">
+        <v>172</v>
+      </c>
+      <c r="F49" t="s">
+        <v>175</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>156</v>
+      </c>
+      <c r="B50" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50">
+        <v>13965</v>
+      </c>
+      <c r="D50">
+        <v>70</v>
+      </c>
+      <c r="E50" t="s">
+        <v>172</v>
+      </c>
+      <c r="F50" t="s">
+        <v>176</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
